--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>FR items of the FRS v1.1</t>
+          <t>FR items of the FRS v1.2</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Standard capability or configuration</t>
+          <t>Standard capability or configuration of the iNXT BrokerVerse platform edition</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>What BIBS offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -965,7 +965,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1326,7 +1326,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1927,7 +1927,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -58795,7 +58795,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -58857,7 +58857,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_FitGap_BRD-06_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -58793,7 +58793,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs Out-of-the-Box vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
